--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F7441B-FB22-4A36-AD1E-A2D935450959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B95FB5D-9B8B-4D8D-BF81-F0AEBA6E44C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1200" windowWidth="21600" windowHeight="13470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="21">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -151,12 +151,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,9 +177,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -493,14 +500,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.3</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -555,14 +562,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.42499999999999999</v>
+        <v>0.57499999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -611,7 +618,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -868,59 +875,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1489,7 +1556,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1747,59 +1814,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B95FB5D-9B8B-4D8D-BF81-F0AEBA6E44C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD56ACB-0B5E-49FB-AB6C-392A2B00D52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6225" yWindow="435" windowWidth="21600" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="28">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -128,6 +128,34 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -500,14 +528,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.53333333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -516,14 +544,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36666666666666664</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -532,14 +560,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -562,14 +590,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.57499999999999996</v>
+        <v>0.82499999999999996</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -594,14 +622,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.3125</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -612,13 +640,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -990,298 +1018,487 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1556,7 +1773,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1929,292 +2146,472 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2222,11 +2619,23 @@
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3">

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD56ACB-0B5E-49FB-AB6C-392A2B00D52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E50CA2-8960-499A-9FAF-F71212DCE61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6225" yWindow="435" windowWidth="21600" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="90" windowWidth="21600" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="28">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -544,14 +544,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.36666666666666664</v>
+        <v>0.6333333333333333</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -606,14 +606,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -646,7 +646,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1143,53 +1143,107 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1773,7 +1827,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2271,71 +2325,143 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E50CA2-8960-499A-9FAF-F71212DCE61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D645D7-70E1-4693-8E05-2AD5C0FA821B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="90" windowWidth="21600" windowHeight="13470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="195" windowWidth="21600" windowHeight="13470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -156,6 +156,22 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -544,14 +560,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.6333333333333333</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -622,14 +638,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -646,7 +662,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1251,53 +1267,107 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
+      <c r="B54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1827,7 +1897,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2469,35 +2539,71 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3">

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D645D7-70E1-4693-8E05-2AD5C0FA821B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068E22BF-6B4B-4112-871D-00EC0AA3AA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="195" windowWidth="21600" windowHeight="13470" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="1440" windowWidth="21600" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$C$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">reading!$A$2:$C$102</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -656,6 +657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -676,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -687,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -699,18 +701,18 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
+      <c r="A5" s="2">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
@@ -722,7 +724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -734,7 +736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -746,7 +748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -758,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -771,18 +773,18 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -794,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -806,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -818,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -831,18 +833,18 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -854,7 +856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -866,7 +868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -878,7 +880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -890,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -902,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -926,7 +928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -938,7 +940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -950,7 +952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -962,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -974,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -986,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1010,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1034,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1046,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1058,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1070,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1106,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1118,7 +1120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1130,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1142,7 +1144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1154,7 +1156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1166,7 +1168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1190,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1202,7 +1204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1214,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1226,7 +1228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1238,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1250,7 +1252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -1262,7 +1264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -1274,7 +1276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -1286,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -1310,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -1322,7 +1324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -1334,7 +1336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -1346,7 +1348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -1358,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -1370,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -1382,7 +1384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -1394,7 +1396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -1406,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -1418,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -1430,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -1442,7 +1444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -1454,7 +1456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -1466,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" hidden="1">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -1478,7 +1480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" hidden="1">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
@@ -1490,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -1517,7 +1519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -1541,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -1553,7 +1555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -1565,7 +1567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -1577,7 +1579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -1613,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -1625,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -1637,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -1649,7 +1651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -1661,7 +1663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -1673,7 +1675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -1685,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -1697,7 +1699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -1709,7 +1711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -1745,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -1757,7 +1759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -1769,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -1781,7 +1783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -1793,7 +1795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -1805,7 +1807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -1817,7 +1819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -1829,7 +1831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -1841,7 +1843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -1853,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -1865,7 +1867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -1878,7 +1880,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:C102" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{14B9F633-8D16-4C6A-BDBF-F784015327B4}">
@@ -1891,6 +1899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -1911,7 +1920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>101</v>
       </c>
@@ -1922,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -1934,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
@@ -1958,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -1970,7 +1979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -1982,7 +1991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -1994,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -2006,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -2018,7 +2027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -2030,7 +2039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -2042,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -2054,7 +2063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
@@ -2066,7 +2075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
@@ -2078,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -2090,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -2114,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -2138,7 +2147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
@@ -2162,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -2174,7 +2183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -2186,7 +2195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
@@ -2210,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -2234,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -2258,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" hidden="1">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
@@ -2270,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -2282,7 +2291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
@@ -2294,7 +2303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
@@ -2306,7 +2315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
@@ -2318,7 +2327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
@@ -2330,7 +2339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" hidden="1">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
@@ -2342,7 +2351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
@@ -2354,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
@@ -2366,7 +2375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
@@ -2378,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
@@ -2402,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
@@ -2414,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
@@ -2426,7 +2435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
@@ -2438,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
@@ -2450,7 +2459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
@@ -2462,7 +2471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
@@ -2474,7 +2483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
@@ -2498,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
@@ -2510,7 +2519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
@@ -2522,7 +2531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
@@ -2534,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
@@ -2546,7 +2555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
@@ -2558,7 +2567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
@@ -2582,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
@@ -2606,7 +2615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
@@ -2618,7 +2627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
@@ -2630,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
@@ -2642,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
@@ -2654,7 +2663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
@@ -2678,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
@@ -2690,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
@@ -2702,7 +2711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
@@ -2714,7 +2723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
@@ -2726,7 +2735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
@@ -2738,7 +2747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -2750,7 +2759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
@@ -2762,7 +2771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
@@ -2774,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
@@ -2786,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
@@ -2798,7 +2807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
@@ -2810,7 +2819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
@@ -2822,7 +2831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
@@ -2834,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
@@ -2846,7 +2855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
@@ -2858,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -2870,7 +2879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
@@ -2882,7 +2891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
@@ -2894,7 +2903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
@@ -2918,7 +2927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
@@ -2942,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
@@ -2966,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
@@ -2978,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
@@ -2990,7 +2999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
@@ -3002,7 +3011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
@@ -3014,7 +3023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
@@ -3026,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
@@ -3038,7 +3047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
@@ -3062,7 +3071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
@@ -3086,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
@@ -3098,7 +3107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -3111,6 +3120,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">
@@ -3123,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C2"/>
+  <dimension ref="A2:C8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3135,6 +3151,72 @@
       </c>
       <c r="C2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>104</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>117</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>119</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068E22BF-6B4B-4112-871D-00EC0AA3AA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8683E3F9-6125-462C-86EA-E88850E95F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1440" windowWidth="21600" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8415" yWindow="840" windowWidth="21600" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3139,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C8"/>
+  <dimension ref="A2:C18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3216,6 +3216,116 @@
         <v>8</v>
       </c>
       <c r="C8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>121</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>125</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>127</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>129</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>141</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8683E3F9-6125-462C-86EA-E88850E95F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E879224-4BE6-4353-BE76-110E3361C1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8415" yWindow="840" windowWidth="21600" windowHeight="13470" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -917,14 +917,14 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1001,14 +1001,14 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1025,14 +1025,14 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32">
+      <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1085,26 +1085,26 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37">
+      <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38">
+      <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C18"/>
+  <dimension ref="A2:C29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3329,10 +3329,131 @@
         <v>1</v>
       </c>
     </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>55</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>147</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>148</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>149</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>155</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>156</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E879224-4BE6-4353-BE76-110E3361C1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CB7CEF-18AD-4988-8894-541D0F8A059B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="885" windowWidth="15225" windowHeight="13875" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3139,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C29"/>
+  <dimension ref="A2:C40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3450,10 +3450,131 @@
         <v>1</v>
       </c>
     </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>70</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>71</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>73</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>157</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>158</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>162</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>163</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>164</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B32" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B29" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04CB7CEF-18AD-4988-8894-541D0F8A059B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2AB6FA-524D-489A-8FA2-8323155804A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="885" windowWidth="15225" windowHeight="13875" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3139,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C40"/>
+  <dimension ref="A2:C48"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3568,6 +3568,98 @@
         <v>9</v>
       </c>
       <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>77</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>78</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>79</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>181</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <f>A44+1</f>
+        <v>182</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <f t="shared" ref="A46:A48" si="0">A45+1</f>
+        <v>183</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>184</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2AB6FA-524D-489A-8FA2-8323155804A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C4B8D9-E15A-4F77-A883-96A02E9DB221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3139,7 +3139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C48"/>
+  <dimension ref="A2:C56"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3660,6 +3660,98 @@
         <v>8</v>
       </c>
       <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>86</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>87</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>88</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>186</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <f>A52+1</f>
+        <v>187</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <f t="shared" ref="A54:A56" si="1">A53+1</f>
+        <v>188</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <f t="shared" si="1"/>
+        <v>189</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial2-v1.xlsx
+++ b/toeic-test-v5/trial2-v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C4B8D9-E15A-4F77-A883-96A02E9DB221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB92FDD7-EA22-4146-94B2-D9417948E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="570" windowWidth="15225" windowHeight="13875" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -222,10 +222,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3139,7 +3140,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:C56"/>
+  <dimension ref="A2:C65"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:3">
@@ -3755,10 +3756,109 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="3">
+        <v>3</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3">
+        <v>9</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3">
+        <v>14</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3">
+        <v>21</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3">
+        <v>196</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>197</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>198</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>199</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>200</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B29" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B21:B24 B27:B29 B57:B60" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>
